--- a/artfynd/S 1177-2022 artfynd.xlsx
+++ b/artfynd/S 1177-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AZ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134573600</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4640</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081305</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081306</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1233,6 +1258,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081307</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081308</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1453,6 +1488,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081309</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1563,6 +1603,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081310</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1693,6 +1738,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105553866</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1823,6 +1873,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105553868</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1948,6 +2003,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113474431</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2073,6 +2133,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113474432</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2198,6 +2263,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113474433</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2323,6 +2393,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113474434</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2448,6 +2523,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768545</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2573,6 +2653,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768546</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2698,6 +2783,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768549</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2823,6 +2913,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768550</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2948,6 +3043,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768554</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3073,6 +3173,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768555</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3183,6 +3288,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081292</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3293,6 +3403,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081293</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3403,6 +3518,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081294</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3513,6 +3633,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081295</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3623,6 +3748,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081297</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3733,6 +3863,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081299</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3843,6 +3978,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97081300</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3973,6 +4113,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105553842</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4103,6 +4248,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105553862</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4228,6 +4378,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768523</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4353,6 +4508,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768525</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4478,6 +4638,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768527</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4603,6 +4768,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768543</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4728,6 +4898,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120768544</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4858,6 +5033,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129834613</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4988,6 +5168,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129834614</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5118,6 +5303,11 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129834615</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5248,8 +5438,53 @@
           <t>Biogeografisk uppföljning av fjärilar</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129834616</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>